--- a/AAII_Financials/Yearly/NXXT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NXXT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>NXXT</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,14 +693,14 @@
       <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44196</v>
-      </c>
-      <c r="J7" s="2">
-        <v>43830</v>
+      <c r="H7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -720,20 +720,20 @@
       <c r="E8" s="3">
         <v>27800</v>
       </c>
-      <c r="F8" s="3">
-        <v>23200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>15000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1600</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -753,20 +753,20 @@
       <c r="E9" s="3">
         <v>26000</v>
       </c>
-      <c r="F9" s="3">
-        <v>21800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>15200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1500</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -786,20 +786,20 @@
       <c r="E10" s="3">
         <v>1800</v>
       </c>
-      <c r="F10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -895,16 +895,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>17900</v>
+        <v>8500</v>
       </c>
       <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
-        <v>300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -934,19 +934,19 @@
         <v>1500</v>
       </c>
       <c r="F15" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>135000</v>
+        <v>143500</v>
       </c>
       <c r="E17" s="3">
         <v>39500</v>
       </c>
       <c r="F17" s="3">
-        <v>31700</v>
+        <v>700</v>
       </c>
       <c r="G17" s="3">
-        <v>32500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>16000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>10500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2500</v>
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-53100</v>
+        <v>-61700</v>
       </c>
       <c r="E18" s="3">
         <v>-11700</v>
       </c>
       <c r="F18" s="3">
-        <v>-8500</v>
+        <v>-700</v>
       </c>
       <c r="G18" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-600</v>
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-200</v>
+        <v>700</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>-100</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
-        <v>-200</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-50300</v>
+        <v>-59700</v>
       </c>
       <c r="E21" s="3">
         <v>-9800</v>
       </c>
       <c r="F21" s="3">
-        <v>-7400</v>
+        <v>-700</v>
       </c>
       <c r="G21" s="3">
-        <v>-15700</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>-7700</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1126,19 +1126,19 @@
         <v>9400</v>
       </c>
       <c r="F22" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1159,19 +1159,19 @@
         <v>-21400</v>
       </c>
       <c r="F23" s="3">
-        <v>-10500</v>
+        <v>-600</v>
       </c>
       <c r="G23" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1258,19 +1258,19 @@
         <v>-21400</v>
       </c>
       <c r="F26" s="3">
-        <v>-10500</v>
+        <v>-600</v>
       </c>
       <c r="G26" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1291,19 +1291,19 @@
         <v>-21600</v>
       </c>
       <c r="F27" s="3">
-        <v>-10500</v>
+        <v>-600</v>
       </c>
       <c r="G27" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>200</v>
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>100</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
-        <v>200</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1489,19 +1489,19 @@
         <v>-21400</v>
       </c>
       <c r="F33" s="3">
-        <v>-10500</v>
+        <v>-600</v>
       </c>
       <c r="G33" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1555,19 +1555,19 @@
         <v>-21400</v>
       </c>
       <c r="F35" s="3">
-        <v>-10500</v>
+        <v>-600</v>
       </c>
       <c r="G35" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1598,14 +1598,14 @@
       <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44196</v>
-      </c>
-      <c r="J38" s="2">
-        <v>43830</v>
+      <c r="H38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1656,19 +1656,19 @@
         <v>1600</v>
       </c>
       <c r="F41" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G41" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H41" s="3">
-        <v>13600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1692,10 +1692,10 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1722,19 +1722,19 @@
         <v>1600</v>
       </c>
       <c r="F43" s="3">
-        <v>1200</v>
+        <v>2600</v>
       </c>
       <c r="G43" s="3">
-        <v>800</v>
-      </c>
-      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
-        <v>200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1754,20 +1754,20 @@
       <c r="E44" s="3">
         <v>100</v>
       </c>
-      <c r="F44" s="3">
-        <v>100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>200</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1787,8 +1787,8 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+      <c r="F45" s="3">
+        <v>300</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1796,11 +1796,11 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1821,19 +1821,19 @@
         <v>3400</v>
       </c>
       <c r="F46" s="3">
-        <v>1800</v>
+        <v>3400</v>
       </c>
       <c r="G46" s="3">
-        <v>5400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>17300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J46" s="3">
         <v>100</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1887,19 +1887,19 @@
         <v>7900</v>
       </c>
       <c r="F48" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
+        <v>100</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1925,14 +1925,14 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>700</v>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2018,14 +2018,14 @@
       <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2085,19 +2085,19 @@
         <v>22400</v>
       </c>
       <c r="F54" s="3">
-        <v>5700</v>
+        <v>3500</v>
       </c>
       <c r="G54" s="3">
-        <v>10600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>22900</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1200</v>
+        <v>100</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2148,19 +2148,19 @@
         <v>1700</v>
       </c>
       <c r="F57" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2181,19 +2181,19 @@
         <v>31200</v>
       </c>
       <c r="F58" s="3">
-        <v>6100</v>
+        <v>3900</v>
       </c>
       <c r="G58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
@@ -2222,8 +2222,8 @@
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
-        <v>1100</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2247,19 +2247,19 @@
         <v>34700</v>
       </c>
       <c r="F60" s="3">
-        <v>7000</v>
+        <v>3900</v>
       </c>
       <c r="G60" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2280,19 +2280,19 @@
         <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2445,19 +2445,19 @@
         <v>35100</v>
       </c>
       <c r="F66" s="3">
-        <v>7600</v>
+        <v>3900</v>
       </c>
       <c r="G66" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>800</v>
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2625,19 +2625,19 @@
         <v>-67500</v>
       </c>
       <c r="F72" s="3">
-        <v>-45300</v>
+        <v>-600</v>
       </c>
       <c r="G72" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2757,19 +2757,19 @@
         <v>-12700</v>
       </c>
       <c r="F76" s="3">
-        <v>-1900</v>
+        <v>-500</v>
       </c>
       <c r="G76" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H76" s="3">
-        <v>21900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2833,14 +2833,14 @@
       <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44196</v>
-      </c>
-      <c r="J80" s="2">
-        <v>43830</v>
+      <c r="H80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2861,19 +2861,19 @@
         <v>-21400</v>
       </c>
       <c r="F81" s="3">
-        <v>-10500</v>
+        <v>-600</v>
       </c>
       <c r="G81" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-700</v>
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2906,22 +2906,22 @@
         <v>1600</v>
       </c>
       <c r="E83" s="3">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3107,19 +3107,19 @@
         <v>-6300</v>
       </c>
       <c r="F89" s="3">
-        <v>-6600</v>
+        <v>-700</v>
       </c>
       <c r="G89" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-500</v>
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3152,22 +3152,22 @@
         <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-11700</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3254,19 +3254,19 @@
         <v>-11700</v>
       </c>
       <c r="F94" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-200</v>
+        <v>-2600</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3434,19 +3434,19 @@
         <v>18500</v>
       </c>
       <c r="F100" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H100" s="3">
-        <v>24400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J100" s="3">
-        <v>1000</v>
+        <v>3800</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3500,19 +3500,19 @@
         <v>600</v>
       </c>
       <c r="F102" s="3">
-        <v>-1800</v>
+        <v>500</v>
       </c>
       <c r="G102" s="3">
-        <v>-11500</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>12700</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
